--- a/artfynd/A 34059-2025 artfynd.xlsx
+++ b/artfynd/A 34059-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ11"/>
+  <dimension ref="A1:AZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>135638727</v>
       </c>
       <c r="B2" t="n">
-        <v>97479</v>
+        <v>97506</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135639940</v>
       </c>
       <c r="B3" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1380,53 +1380,56 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135638171</v>
+        <v>135693507</v>
       </c>
       <c r="B8" t="n">
-        <v>57167</v>
+        <v>57980</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Långtjärnen, Långtjärnen, Vstm</t>
+          <t>långtjärn, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>489394</v>
+        <v>489391</v>
       </c>
       <c r="R8" t="n">
-        <v>6617707</v>
+        <v>6617560</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1455,7 +1458,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1465,7 +1468,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack. Foto finns</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1480,27 +1488,27 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135638171</t>
+          <t>https://artportalen.se/Sighting/135693507</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135657399</v>
+        <v>135638171</v>
       </c>
       <c r="B9" t="n">
-        <v>5181</v>
+        <v>57167</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1508,42 +1516,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100526</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Långtjärn, Vstm</t>
+          <t>Långtjärnen, Långtjärnen, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>489368</v>
+        <v>489394</v>
       </c>
       <c r="R9" t="n">
-        <v>6617656</v>
+        <v>6617707</v>
       </c>
       <c r="S9" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1570,14 +1578,19 @@
           <t>2026-08-04</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Gnag</t>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1586,34 +1599,33 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135657399</t>
+          <t>https://artportalen.se/Sighting/135638171</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135657404</v>
+        <v>135692405</v>
       </c>
       <c r="B10" t="n">
-        <v>5181</v>
+        <v>57167</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1621,30 +1633,29 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100526</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1654,13 +1665,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>489453</v>
+        <v>489366</v>
       </c>
       <c r="R10" t="n">
-        <v>6617605</v>
+        <v>6617669</v>
       </c>
       <c r="S10" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1687,14 +1698,24 @@
           <t>2026-08-04</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Spår, gnag i tunn gran</t>
+          <t>Sandbad m spillning</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1703,34 +1724,33 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135657404</t>
+          <t>https://artportalen.se/Sighting/135692405</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135657401</v>
+        <v>135692514</v>
       </c>
       <c r="B11" t="n">
-        <v>58136</v>
+        <v>57167</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1738,27 +1758,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103023</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1766,13 +1790,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>489409</v>
+        <v>489372</v>
       </c>
       <c r="R11" t="n">
-        <v>6617624</v>
+        <v>6617674</v>
       </c>
       <c r="S11" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1799,14 +1823,19 @@
           <t>2026-08-04</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Lockläte</t>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1821,16 +1850,1107 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135692514</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135692614</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Långtjärn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>489359</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6617601</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Hjulsjö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Spillning på sten</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135692614</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135692793</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Långtjärn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>489359</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6617580</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Hjulsjö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Sandbad i hygget</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135692793</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135693122</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Långtjärn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>489507</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6617594</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Hjulsjö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På sten</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135693122</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135693131</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Långtjärn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>489513</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6617602</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Hjulsjö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På sten</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135693131</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135693144</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Långtjärn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>489511</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6617611</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Hjulsjö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På sten</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135693144</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135693488</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>långtjärn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>489393</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6617569</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Hjulsjö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Sandbad</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135693488</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135657399</v>
+      </c>
+      <c r="B18" t="n">
+        <v>5181</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Långtjärn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>489368</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6617656</v>
+      </c>
+      <c r="S18" t="n">
+        <v>7</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Hjulsjö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Gnag</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Mattias Drejby</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Mattias Drejby</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135657399</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135657404</v>
+      </c>
+      <c r="B19" t="n">
+        <v>5181</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Långtjärn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>489453</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6617605</v>
+      </c>
+      <c r="S19" t="n">
+        <v>7</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Hjulsjö</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Spår, gnag i tunn gran</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Mattias Drejby</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Mattias Drejby</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135657404</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135657401</v>
+      </c>
+      <c r="B20" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Långtjärn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>489409</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6617624</v>
+      </c>
+      <c r="S20" t="n">
+        <v>68</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Hjulsjö</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Lockläte</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Mattias Drejby</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Mattias Drejby</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135657401</t>
         </is>
@@ -1848,6 +2968,15 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34059-2025 artfynd.xlsx
+++ b/artfynd/A 34059-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135638727</v>
       </c>
       <c r="B2" t="n">
-        <v>97511</v>
+        <v>97513</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34059-2025 artfynd.xlsx
+++ b/artfynd/A 34059-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135638727</v>
       </c>
       <c r="B2" t="n">
-        <v>97513</v>
+        <v>97530</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135639940</v>
       </c>
       <c r="B3" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135640184</v>
       </c>
       <c r="B4" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>135640365</v>
       </c>
       <c r="B5" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>135640496</v>
       </c>
       <c r="B6" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>135638476</v>
       </c>
       <c r="B7" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1383,7 +1383,7 @@
         <v>135693507</v>
       </c>
       <c r="B8" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         <v>135638171</v>
       </c>
       <c r="B9" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1625,7 +1625,7 @@
         <v>135692405</v>
       </c>
       <c r="B10" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>135692514</v>
       </c>
       <c r="B11" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>135692614</v>
       </c>
       <c r="B12" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
         <v>135692793</v>
       </c>
       <c r="B13" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>135693122</v>
       </c>
       <c r="B14" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         <v>135693131</v>
       </c>
       <c r="B15" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2370,7 +2370,7 @@
         <v>135693144</v>
       </c>
       <c r="B16" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         <v>135693488</v>
       </c>
       <c r="B17" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2620,7 +2620,7 @@
         <v>135657399</v>
       </c>
       <c r="B18" t="n">
-        <v>5181</v>
+        <v>5182</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
         <v>135657404</v>
       </c>
       <c r="B19" t="n">
-        <v>5181</v>
+        <v>5182</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2850,7 +2850,7 @@
         <v>135657401</v>
       </c>
       <c r="B20" t="n">
-        <v>58136</v>
+        <v>58138</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 34059-2025 artfynd.xlsx
+++ b/artfynd/A 34059-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135638727</v>
       </c>
       <c r="B2" t="n">
-        <v>97530</v>
+        <v>97531</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135639940</v>
       </c>
       <c r="B3" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34059-2025 artfynd.xlsx
+++ b/artfynd/A 34059-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135638727</v>
       </c>
       <c r="B2" t="n">
-        <v>97531</v>
+        <v>97532</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34059-2025 artfynd.xlsx
+++ b/artfynd/A 34059-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135638727</v>
       </c>
       <c r="B2" t="n">
-        <v>97532</v>
+        <v>97533</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135639940</v>
       </c>
       <c r="B3" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135640184</v>
       </c>
       <c r="B4" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>135640365</v>
       </c>
       <c r="B5" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>135640496</v>
       </c>
       <c r="B6" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>135638476</v>
       </c>
       <c r="B7" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1383,7 +1383,7 @@
         <v>135693507</v>
       </c>
       <c r="B8" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         <v>135638171</v>
       </c>
       <c r="B9" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1625,7 +1625,7 @@
         <v>135692405</v>
       </c>
       <c r="B10" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>135692514</v>
       </c>
       <c r="B11" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>135692614</v>
       </c>
       <c r="B12" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
         <v>135692793</v>
       </c>
       <c r="B13" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>135693122</v>
       </c>
       <c r="B14" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         <v>135693131</v>
       </c>
       <c r="B15" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2370,7 +2370,7 @@
         <v>135693144</v>
       </c>
       <c r="B16" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         <v>135693488</v>
       </c>
       <c r="B17" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2850,7 +2850,7 @@
         <v>135657401</v>
       </c>
       <c r="B20" t="n">
-        <v>58138</v>
+        <v>58139</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 34059-2025 artfynd.xlsx
+++ b/artfynd/A 34059-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135638727</v>
       </c>
       <c r="B2" t="n">
-        <v>97533</v>
+        <v>97539</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135639940</v>
       </c>
       <c r="B3" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135640184</v>
       </c>
       <c r="B4" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>135640365</v>
       </c>
       <c r="B5" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>135640496</v>
       </c>
       <c r="B6" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>135638476</v>
       </c>
       <c r="B7" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1383,7 +1383,7 @@
         <v>135693507</v>
       </c>
       <c r="B8" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         <v>135638171</v>
       </c>
       <c r="B9" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1625,7 +1625,7 @@
         <v>135692405</v>
       </c>
       <c r="B10" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>135692514</v>
       </c>
       <c r="B11" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>135692614</v>
       </c>
       <c r="B12" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
         <v>135692793</v>
       </c>
       <c r="B13" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>135693122</v>
       </c>
       <c r="B14" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         <v>135693131</v>
       </c>
       <c r="B15" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2370,7 +2370,7 @@
         <v>135693144</v>
       </c>
       <c r="B16" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         <v>135693488</v>
       </c>
       <c r="B17" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2850,7 +2850,7 @@
         <v>135657401</v>
       </c>
       <c r="B20" t="n">
-        <v>58139</v>
+        <v>58143</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 34059-2025 artfynd.xlsx
+++ b/artfynd/A 34059-2025 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>135640184</v>
       </c>
       <c r="B4" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>135640365</v>
       </c>
       <c r="B5" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>135640496</v>
       </c>
       <c r="B6" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>135638476</v>
       </c>
       <c r="B7" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1383,7 +1383,7 @@
         <v>135693507</v>
       </c>
       <c r="B8" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         <v>135638171</v>
       </c>
       <c r="B9" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1625,7 +1625,7 @@
         <v>135692405</v>
       </c>
       <c r="B10" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>135692514</v>
       </c>
       <c r="B11" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>135692614</v>
       </c>
       <c r="B12" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
         <v>135692793</v>
       </c>
       <c r="B13" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>135693122</v>
       </c>
       <c r="B14" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         <v>135693131</v>
       </c>
       <c r="B15" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2370,7 +2370,7 @@
         <v>135693144</v>
       </c>
       <c r="B16" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         <v>135693488</v>
       </c>
       <c r="B17" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2850,7 +2850,7 @@
         <v>135657401</v>
       </c>
       <c r="B20" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 34059-2025 artfynd.xlsx
+++ b/artfynd/A 34059-2025 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>135640184</v>
       </c>
       <c r="B4" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>135640365</v>
       </c>
       <c r="B5" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>135640496</v>
       </c>
       <c r="B6" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>135638476</v>
       </c>
       <c r="B7" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1383,7 +1383,7 @@
         <v>135693507</v>
       </c>
       <c r="B8" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         <v>135638171</v>
       </c>
       <c r="B9" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1625,7 +1625,7 @@
         <v>135692405</v>
       </c>
       <c r="B10" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>135692514</v>
       </c>
       <c r="B11" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>135692614</v>
       </c>
       <c r="B12" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
         <v>135692793</v>
       </c>
       <c r="B13" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>135693122</v>
       </c>
       <c r="B14" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         <v>135693131</v>
       </c>
       <c r="B15" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2370,7 +2370,7 @@
         <v>135693144</v>
       </c>
       <c r="B16" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         <v>135693488</v>
       </c>
       <c r="B17" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2850,7 +2850,7 @@
         <v>135657401</v>
       </c>
       <c r="B20" t="n">
-        <v>58144</v>
+        <v>58149</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 34059-2025 artfynd.xlsx
+++ b/artfynd/A 34059-2025 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>135640184</v>
       </c>
       <c r="B4" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>135640365</v>
       </c>
       <c r="B5" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>135640496</v>
       </c>
       <c r="B6" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>135638476</v>
       </c>
       <c r="B7" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1383,7 +1383,7 @@
         <v>135693507</v>
       </c>
       <c r="B8" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         <v>135638171</v>
       </c>
       <c r="B9" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1625,7 +1625,7 @@
         <v>135692405</v>
       </c>
       <c r="B10" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>135692514</v>
       </c>
       <c r="B11" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>135692614</v>
       </c>
       <c r="B12" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
         <v>135692793</v>
       </c>
       <c r="B13" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>135693122</v>
       </c>
       <c r="B14" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         <v>135693131</v>
       </c>
       <c r="B15" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2370,7 +2370,7 @@
         <v>135693144</v>
       </c>
       <c r="B16" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         <v>135693488</v>
       </c>
       <c r="B17" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2850,7 +2850,7 @@
         <v>135657401</v>
       </c>
       <c r="B20" t="n">
-        <v>58149</v>
+        <v>58162</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
